--- a/Sacramento_Kings_2025-26_stats.xlsx
+++ b/Sacramento_Kings_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1246,66 @@
       </c>
       <c r="R13" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>34</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,6 +2132,66 @@
       </c>
       <c r="R13" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2898,6 +3018,66 @@
       </c>
       <c r="R13" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3903,66 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3759,7 +3999,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -3769,7 +4009,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.16666666666667</v>
+        <v>18.15384615384615</v>
       </c>
     </row>
     <row r="4">
@@ -3779,7 +4019,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.33333333333333</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="5">
@@ -3789,7 +4029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.5</v>
+        <v>14.38461538461539</v>
       </c>
     </row>
     <row r="6">
@@ -3799,7 +4039,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.22222222222222</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="7">
@@ -3809,7 +4049,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.33333333333333</v>
+        <v>11.53846153846154</v>
       </c>
     </row>
     <row r="8">
@@ -3819,27 +4059,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.333333333333333</v>
+        <v>7.461538461538462</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Drew Eubanks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.2</v>
+        <v>6.692307692307693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drew Eubanks</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.833333333333333</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3859,7 +4099,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.75</v>
+        <v>5.111111111111111</v>
       </c>
     </row>
     <row r="13">
@@ -3941,21 +4181,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Russell Westbrook</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>6.384615384615385</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Russell Westbrook</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3965,7 +4205,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.666666666666667</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -3975,7 +4215,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.333333333333333</v>
+        <v>3.461538461538462</v>
       </c>
     </row>
     <row r="6">
@@ -3985,7 +4225,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.625</v>
+        <v>2.444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -3995,7 +4235,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.444444444444445</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -4005,7 +4245,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1</v>
+        <v>2.181818181818182</v>
       </c>
     </row>
     <row r="9">
@@ -4025,7 +4265,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -4035,7 +4275,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.75</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -4065,7 +4305,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="15">
@@ -4131,7 +4371,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.33333333333333</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3">
@@ -4141,7 +4381,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.166666666666667</v>
+        <v>6.461538461538462</v>
       </c>
     </row>
     <row r="4">
@@ -4151,57 +4391,57 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.75</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.666666666666667</v>
+        <v>3.636363636363636</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.416666666666667</v>
+        <v>3.461538461538462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4</v>
+        <v>3.384615384615385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dennis Schröder</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.25</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -4211,7 +4451,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.916666666666667</v>
+        <v>2.923076923076923</v>
       </c>
     </row>
     <row r="11">
@@ -4251,7 +4491,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.583333333333333</v>
+        <v>1.538461538461539</v>
       </c>
     </row>
     <row r="15">
@@ -4261,7 +4501,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.555555555555556</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -4317,27 +4557,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.3</v>
+        <v>3.363636363636364</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Russell Westbrook</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.222222222222222</v>
+        <v>2.076923076923077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Russell Westbrook</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.083333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4357,7 +4597,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.75</v>
+        <v>1.846153846153846</v>
       </c>
     </row>
     <row r="7">
@@ -4367,7 +4607,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.25</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="8">
@@ -4377,7 +4617,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="9">
@@ -4387,23 +4627,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dario Šarić</t>
+          <t>Domantas Sabonis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Domantas Sabonis</t>
+          <t>Dario Šarić</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4481,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4763,6 +5003,27 @@
         <v>233</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>110</v>
+      </c>
+      <c r="D14" t="n">
+        <v>124</v>
+      </c>
+      <c r="E14" t="n">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
